--- a/output/daily_ratings/uk_ratings_2026-06-23.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-06-23.xlsx
@@ -524,11 +524,11 @@
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Rogue Passion (IRE)</t>
+          <t>Lady Caroline Lamb</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -544,14 +544,16 @@
       <c r="M2" t="n">
         <v>92.86</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>72.7</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -580,11 +582,11 @@
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lady Caroline Lamb</t>
+          <t>Little Lady Karen</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -596,12 +598,14 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M3" t="n">
         <v>92.86</v>
       </c>
       <c r="N3" t="n">
-        <v>72.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -638,30 +642,30 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Little Lady Karen</t>
+          <t>Fern Clyde</t>
         </is>
       </c>
       <c r="I4" t="n">
         <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>6.75</v>
       </c>
       <c r="M4" t="n">
         <v>92.86</v>
       </c>
       <c r="N4" t="n">
-        <v>67.09999999999999</v>
+        <v>57.1</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -698,34 +702,34 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Fern Clyde</t>
+          <t>Cousin Rachel</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6.75</v>
+        <v>21.75</v>
       </c>
       <c r="M5" t="n">
         <v>92.86</v>
       </c>
       <c r="N5" t="n">
-        <v>57.1</v>
+        <v>17.6</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -757,40 +761,24 @@
       <c r="F6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>4</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Cousin Rachel</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>128</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>21.75</v>
-      </c>
-      <c r="M6" t="n">
-        <v>92.86</v>
-      </c>
-      <c r="N6" t="n">
-        <v>17.6</v>
-      </c>
+          <t>Rogue Passion (IRE)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -818,34 +806,36 @@
         <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Evocative Spark (IRE)</t>
+          <t>Tattie Bogle</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K7" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>91.93000000000001</v>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>69.8</v>
+      </c>
       <c r="O7" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -874,15 +864,15 @@
         <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Tattie Bogle</t>
+          <t>Coolree (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J8" t="n">
         <v>135</v>
@@ -890,12 +880,14 @@
       <c r="K8" t="n">
         <v>68</v>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M8" t="n">
         <v>91.93000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>69.8</v>
+        <v>64.5</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -903,7 +895,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
@@ -932,30 +924,30 @@
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Coolree (IRE)</t>
+          <t>Roaring Ralph</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>135</v>
       </c>
       <c r="K9" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="L9" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="M9" t="n">
         <v>91.93000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -963,7 +955,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -992,30 +984,30 @@
         <v>5</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Roaring Ralph</t>
+          <t>Sunny Orange (IRE)</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="K10" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="L10" t="n">
-        <v>1.9</v>
+        <v>5.15</v>
       </c>
       <c r="M10" t="n">
         <v>91.93000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>67.59999999999999</v>
+        <v>48.3</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1023,7 +1015,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="11">
@@ -1052,30 +1044,30 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sunny Orange (IRE)</t>
+          <t>This Farh</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="K11" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="L11" t="n">
-        <v>5.15</v>
+        <v>6.9</v>
       </c>
       <c r="M11" t="n">
         <v>91.93000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>48.3</v>
+        <v>56.2</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1083,7 +1075,7 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1112,30 +1104,30 @@
         <v>5</v>
       </c>
       <c r="G12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>This Farh</t>
+          <t>Midsummer Storm (IRE)</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="K12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L12" t="n">
-        <v>6.9</v>
+        <v>9.65</v>
       </c>
       <c r="M12" t="n">
         <v>91.93000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>56.2</v>
+        <v>48.7</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1171,40 +1163,24 @@
       <c r="F13" t="n">
         <v>5</v>
       </c>
-      <c r="G13" t="n">
-        <v>6</v>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Midsummer Storm (IRE)</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3</v>
-      </c>
-      <c r="J13" t="n">
-        <v>132</v>
-      </c>
-      <c r="K13" t="n">
-        <v>74</v>
-      </c>
-      <c r="L13" t="n">
-        <v>9.65</v>
-      </c>
-      <c r="M13" t="n">
-        <v>91.93000000000001</v>
-      </c>
-      <c r="N13" t="n">
-        <v>48.7</v>
-      </c>
+          <t>Evocative Spark (IRE)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P13" t="n">
-        <v>1</v>
-      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1232,11 +1208,11 @@
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Cherringham</t>
+          <t>Tamzan</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1246,20 +1222,22 @@
         <v>127</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>106.19</v>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>63.6</v>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1288,28 +1266,30 @@
         <v>5</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Tamzan</t>
+          <t>Regal Desire (FR)</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K15" t="n">
-        <v>67</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M15" t="n">
         <v>106.19</v>
       </c>
       <c r="N15" t="n">
-        <v>63.6</v>
+        <v>60.1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1317,7 +1297,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
@@ -1346,30 +1326,30 @@
         <v>5</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Regal Desire (FR)</t>
+          <t>Alterity</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>106.19</v>
       </c>
       <c r="N16" t="n">
-        <v>60.1</v>
+        <v>60.8</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1377,7 +1357,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1406,30 +1386,30 @@
         <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Alterity</t>
+          <t>Pepsea (IRE)</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
         <v>106.19</v>
       </c>
       <c r="N17" t="n">
-        <v>60.8</v>
+        <v>56.3</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1437,7 +1417,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1466,11 +1446,11 @@
         <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Pepsea (IRE)</t>
+          <t>Feliz Navidad</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1480,16 +1460,16 @@
         <v>130</v>
       </c>
       <c r="K18" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>3.5</v>
+        <v>7.25</v>
       </c>
       <c r="M18" t="n">
         <v>106.19</v>
       </c>
       <c r="N18" t="n">
-        <v>56.3</v>
+        <v>47.7</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1526,11 +1506,11 @@
         <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Feliz Navidad</t>
+          <t>Three No Trumps</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1540,16 +1520,16 @@
         <v>130</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="L19" t="n">
-        <v>7.25</v>
+        <v>11.75</v>
       </c>
       <c r="M19" t="n">
         <v>106.19</v>
       </c>
       <c r="N19" t="n">
-        <v>47.7</v>
+        <v>37.2</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1585,40 +1565,24 @@
       <c r="F20" t="n">
         <v>5</v>
       </c>
-      <c r="G20" t="n">
-        <v>6</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Three No Trumps</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>130</v>
-      </c>
-      <c r="K20" t="n">
-        <v>72</v>
-      </c>
-      <c r="L20" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="M20" t="n">
-        <v>106.19</v>
-      </c>
-      <c r="N20" t="n">
-        <v>37.2</v>
-      </c>
+          <t>Cherringham</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1646,34 +1610,36 @@
         <v>6</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Jedhi Knight</t>
+          <t>Satyress</t>
         </is>
       </c>
       <c r="I21" t="n">
         <v>4</v>
       </c>
       <c r="J21" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="K21" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="n">
         <v>158.34</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="n">
+        <v>49.7</v>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>-7.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="22">
@@ -1702,34 +1668,38 @@
         <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Dandys Angel (IRE)</t>
+          <t>Bruce Banner (IRE)</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="K22" t="n">
-        <v>48</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M22" t="n">
         <v>158.34</v>
       </c>
-      <c r="N22" t="inlineStr"/>
+      <c r="N22" t="n">
+        <v>52.7</v>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>-7.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1758,15 +1728,15 @@
         <v>6</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Satyress</t>
+          <t>Arch Legend</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
         <v>127</v>
@@ -1774,12 +1744,14 @@
       <c r="K23" t="n">
         <v>47</v>
       </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="L23" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M23" t="n">
         <v>158.34</v>
       </c>
       <c r="N23" t="n">
-        <v>49.7</v>
+        <v>46.6</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -1787,7 +1759,7 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1816,30 +1788,30 @@
         <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Bruce Banner (IRE)</t>
+          <t>Princess Vivi</t>
         </is>
       </c>
       <c r="I24" t="n">
         <v>4</v>
       </c>
       <c r="J24" t="n">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K24" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5</v>
+        <v>1.35</v>
       </c>
       <c r="M24" t="n">
         <v>158.34</v>
       </c>
       <c r="N24" t="n">
-        <v>52.7</v>
+        <v>45.2</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
@@ -1847,7 +1819,7 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1876,30 +1848,30 @@
         <v>6</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Arch Legend</t>
+          <t>Lednikov</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J25" t="n">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="K25" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="L25" t="n">
-        <v>1.25</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
         <v>158.34</v>
       </c>
       <c r="N25" t="n">
-        <v>46.6</v>
+        <v>44.3</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1907,7 +1879,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1936,30 +1908,30 @@
         <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Princess Vivi</t>
+          <t>Sweet Cicely</t>
         </is>
       </c>
       <c r="I26" t="n">
         <v>4</v>
       </c>
       <c r="J26" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K26" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.35</v>
+        <v>5.1</v>
       </c>
       <c r="M26" t="n">
         <v>158.34</v>
       </c>
       <c r="N26" t="n">
-        <v>45.2</v>
+        <v>36.7</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -1967,7 +1939,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1995,40 +1967,24 @@
       <c r="F27" t="n">
         <v>6</v>
       </c>
-      <c r="G27" t="n">
-        <v>5</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Lednikov</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>8</v>
-      </c>
-      <c r="J27" t="n">
-        <v>134</v>
-      </c>
-      <c r="K27" t="n">
-        <v>54</v>
-      </c>
-      <c r="L27" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="M27" t="n">
-        <v>158.34</v>
-      </c>
-      <c r="N27" t="n">
-        <v>49.5</v>
-      </c>
+          <t>Jedhi Knight</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P27" t="n">
-        <v>2</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2055,40 +2011,24 @@
       <c r="F28" t="n">
         <v>6</v>
       </c>
-      <c r="G28" t="n">
-        <v>6</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Sweet Cicely</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>4</v>
-      </c>
-      <c r="J28" t="n">
-        <v>125</v>
-      </c>
-      <c r="K28" t="n">
-        <v>45</v>
-      </c>
-      <c r="L28" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="M28" t="n">
-        <v>158.34</v>
-      </c>
-      <c r="N28" t="n">
-        <v>36.7</v>
-      </c>
+          <t>Dandys Angel (IRE)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
+      <c r="P28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2414,34 +2354,36 @@
         <v>6</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Eva The Deeva</t>
+          <t>Sahm Naif (IRE)</t>
         </is>
       </c>
       <c r="I34" t="n">
         <v>3</v>
       </c>
       <c r="J34" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="K34" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="n">
         <v>125.81</v>
       </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="N34" t="n">
+        <v>62.6</v>
+      </c>
       <c r="O34" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>-7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2470,34 +2412,38 @@
         <v>6</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ice Show</t>
+          <t>Wadacre Geisha</t>
         </is>
       </c>
       <c r="I35" t="n">
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K35" t="n">
-        <v>58</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.05</v>
+      </c>
       <c r="M35" t="n">
         <v>125.81</v>
       </c>
-      <c r="N35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>59.9</v>
+      </c>
       <c r="O35" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>-7.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2526,28 +2472,30 @@
         <v>6</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sahm Naif (IRE)</t>
+          <t>Resdev Time</t>
         </is>
       </c>
       <c r="I36" t="n">
         <v>3</v>
       </c>
       <c r="J36" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K36" t="n">
-        <v>57</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="L36" t="n">
+        <v>3.05</v>
+      </c>
       <c r="M36" t="n">
         <v>125.81</v>
       </c>
       <c r="N36" t="n">
-        <v>62.6</v>
+        <v>52</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2584,30 +2532,30 @@
         <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Wadacre Geisha</t>
+          <t>Royal Sizzler</t>
         </is>
       </c>
       <c r="I37" t="n">
         <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K37" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L37" t="n">
-        <v>0.05</v>
+        <v>6.05</v>
       </c>
       <c r="M37" t="n">
         <v>125.81</v>
       </c>
       <c r="N37" t="n">
-        <v>59.9</v>
+        <v>44.2</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2644,30 +2592,30 @@
         <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Resdev Time</t>
+          <t>Turton</t>
         </is>
       </c>
       <c r="I38" t="n">
         <v>3</v>
       </c>
       <c r="J38" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K38" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L38" t="n">
-        <v>3.05</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>125.81</v>
       </c>
       <c r="N38" t="n">
-        <v>52</v>
+        <v>41.6</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2704,34 +2652,34 @@
         <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Royal Sizzler</t>
+          <t>King Of Yorkshire (IRE)</t>
         </is>
       </c>
       <c r="I39" t="n">
         <v>3</v>
       </c>
       <c r="J39" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K39" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L39" t="n">
-        <v>6.05</v>
+        <v>63.3</v>
       </c>
       <c r="M39" t="n">
         <v>125.81</v>
       </c>
       <c r="N39" t="n">
-        <v>44.2</v>
+        <v>-31.1</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P39" t="n">
@@ -2763,40 +2711,24 @@
       <c r="F40" t="n">
         <v>6</v>
       </c>
-      <c r="G40" t="n">
-        <v>5</v>
-      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Turton</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>3</v>
-      </c>
-      <c r="J40" t="n">
-        <v>130</v>
-      </c>
-      <c r="K40" t="n">
-        <v>53</v>
-      </c>
-      <c r="L40" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="M40" t="n">
-        <v>125.81</v>
-      </c>
-      <c r="N40" t="n">
-        <v>41.6</v>
-      </c>
+          <t>Ice Show</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2823,40 +2755,24 @@
       <c r="F41" t="n">
         <v>6</v>
       </c>
-      <c r="G41" t="n">
-        <v>6</v>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>King Of Yorkshire (IRE)</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>3</v>
-      </c>
-      <c r="J41" t="n">
-        <v>130</v>
-      </c>
-      <c r="K41" t="n">
-        <v>53</v>
-      </c>
-      <c r="L41" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="M41" t="n">
-        <v>125.81</v>
-      </c>
-      <c r="N41" t="n">
-        <v>-31.1</v>
-      </c>
+          <t>Eva The Deeva</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2884,34 +2800,36 @@
         <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Oasis Cover</t>
+          <t>Tanaka (IRE)</t>
         </is>
       </c>
       <c r="I42" t="n">
         <v>3</v>
       </c>
       <c r="J42" t="n">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="K42" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="n">
         <v>62.35</v>
       </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>56.9</v>
+      </c>
       <c r="O42" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="43">
@@ -2940,28 +2858,30 @@
         <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tanaka (IRE)</t>
+          <t>Jack Rabbit Slims</t>
         </is>
       </c>
       <c r="I43" t="n">
         <v>3</v>
       </c>
       <c r="J43" t="n">
-        <v>121</v>
+        <v>134</v>
       </c>
       <c r="K43" t="n">
-        <v>45</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.03</v>
+      </c>
       <c r="M43" t="n">
         <v>62.35</v>
       </c>
       <c r="N43" t="n">
-        <v>58.9</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2969,7 +2889,7 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2998,30 +2918,30 @@
         <v>6</v>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Jack Rabbit Slims</t>
+          <t>Power Of Chora (IRE)</t>
         </is>
       </c>
       <c r="I44" t="n">
         <v>3</v>
       </c>
       <c r="J44" t="n">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="K44" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="L44" t="n">
-        <v>0.03</v>
+        <v>1.53</v>
       </c>
       <c r="M44" t="n">
         <v>62.35</v>
       </c>
       <c r="N44" t="n">
-        <v>67.90000000000001</v>
+        <v>53.6</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3029,7 +2949,7 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="45">
@@ -3058,30 +2978,30 @@
         <v>6</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Power Of Chora (IRE)</t>
+          <t>Dabbling (IRE)</t>
         </is>
       </c>
       <c r="I45" t="n">
         <v>3</v>
       </c>
       <c r="J45" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K45" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="L45" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="M45" t="n">
         <v>62.35</v>
       </c>
       <c r="N45" t="n">
-        <v>58.2</v>
+        <v>60</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3089,7 +3009,7 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3118,30 +3038,30 @@
         <v>6</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Dabbling (IRE)</t>
+          <t>Sparkling Wine</t>
         </is>
       </c>
       <c r="I46" t="n">
         <v>3</v>
       </c>
       <c r="J46" t="n">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="K46" t="n">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L46" t="n">
-        <v>1.68</v>
+        <v>2.68</v>
       </c>
       <c r="M46" t="n">
         <v>62.35</v>
       </c>
       <c r="N46" t="n">
-        <v>60</v>
+        <v>47.1</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3149,7 +3069,7 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3178,30 +3098,30 @@
         <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sparkling Wine</t>
+          <t>Brain Freeze (IRE)</t>
         </is>
       </c>
       <c r="I47" t="n">
         <v>3</v>
       </c>
       <c r="J47" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="K47" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="L47" t="n">
-        <v>2.68</v>
+        <v>4.93</v>
       </c>
       <c r="M47" t="n">
         <v>62.35</v>
       </c>
       <c r="N47" t="n">
-        <v>47.1</v>
+        <v>45.1</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3209,7 +3129,7 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3237,40 +3157,24 @@
       <c r="F48" t="n">
         <v>6</v>
       </c>
-      <c r="G48" t="n">
-        <v>6</v>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Brain Freeze (IRE)</t>
-        </is>
-      </c>
-      <c r="I48" t="n">
-        <v>3</v>
-      </c>
-      <c r="J48" t="n">
-        <v>130</v>
-      </c>
-      <c r="K48" t="n">
-        <v>54</v>
-      </c>
-      <c r="L48" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="M48" t="n">
-        <v>62.35</v>
-      </c>
-      <c r="N48" t="n">
-        <v>48.2</v>
-      </c>
+          <t>Oasis Cover</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P48" t="n">
-        <v>1</v>
-      </c>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3309,7 +3213,7 @@
         <v>9</v>
       </c>
       <c r="J49" t="n">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="K49" t="n">
         <v>64</v>
@@ -3319,7 +3223,7 @@
         <v>70.16</v>
       </c>
       <c r="N49" t="n">
-        <v>61.2</v>
+        <v>54.3</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3327,7 +3231,7 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="50">
@@ -3567,7 +3471,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3627,7 +3531,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3667,7 +3571,7 @@
         <v>3</v>
       </c>
       <c r="J55" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K55" t="n">
         <v>74</v>
@@ -3679,7 +3583,7 @@
         <v>70.16</v>
       </c>
       <c r="N55" t="n">
-        <v>47.6</v>
+        <v>44.6</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3716,34 +3620,36 @@
         <v>5</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Harrys Halo (IRE)</t>
+          <t>Isle Of Lismore (IRE)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J56" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K56" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="n">
         <v>57.84</v>
       </c>
-      <c r="N56" t="inlineStr"/>
+      <c r="N56" t="n">
+        <v>57.4</v>
+      </c>
       <c r="O56" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3772,28 +3678,30 @@
         <v>5</v>
       </c>
       <c r="G57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Isle Of Lismore (IRE)</t>
+          <t>Brazen Idol</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J57" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K57" t="n">
-        <v>68</v>
-      </c>
-      <c r="L57" t="inlineStr"/>
+        <v>70</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M57" t="n">
         <v>57.84</v>
       </c>
       <c r="N57" t="n">
-        <v>57.4</v>
+        <v>57.2</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3830,30 +3738,30 @@
         <v>5</v>
       </c>
       <c r="G58" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Brazen Idol</t>
+          <t>Hint Of Humour</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J58" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K58" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L58" t="n">
-        <v>0.15</v>
+        <v>1.65</v>
       </c>
       <c r="M58" t="n">
         <v>57.84</v>
       </c>
       <c r="N58" t="n">
-        <v>57.2</v>
+        <v>51.5</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3890,30 +3798,30 @@
         <v>5</v>
       </c>
       <c r="G59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Hint Of Humour</t>
+          <t>Candy Warhol (USA)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J59" t="n">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="K59" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="L59" t="n">
-        <v>1.65</v>
+        <v>5.15</v>
       </c>
       <c r="M59" t="n">
         <v>57.84</v>
       </c>
       <c r="N59" t="n">
-        <v>51.5</v>
+        <v>25.9</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3921,7 +3829,7 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="60">
@@ -3950,30 +3858,30 @@
         <v>5</v>
       </c>
       <c r="G60" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Candy Warhol (USA)</t>
+          <t>Arabian Cobra (IRE)</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J60" t="n">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K60" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="L60" t="n">
-        <v>5.15</v>
+        <v>7.65</v>
       </c>
       <c r="M60" t="n">
         <v>57.84</v>
       </c>
       <c r="N60" t="n">
-        <v>25.9</v>
+        <v>32.5</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3981,7 +3889,7 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -4009,40 +3917,24 @@
       <c r="F61" t="n">
         <v>5</v>
       </c>
-      <c r="G61" t="n">
-        <v>5</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Arabian Cobra (IRE)</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>4</v>
-      </c>
-      <c r="J61" t="n">
-        <v>135</v>
-      </c>
-      <c r="K61" t="n">
-        <v>72</v>
-      </c>
-      <c r="L61" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="M61" t="n">
-        <v>57.84</v>
-      </c>
-      <c r="N61" t="n">
-        <v>32.5</v>
-      </c>
+          <t>Harrys Halo (IRE)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P61" t="n">
-        <v>1</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4439,7 +4331,7 @@
         <v>8</v>
       </c>
       <c r="J68" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="K68" t="n">
         <v>0</v>
@@ -4451,7 +4343,7 @@
         <v>91.89</v>
       </c>
       <c r="N68" t="n">
-        <v>18.2</v>
+        <v>14.1</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4608,18 +4500,18 @@
         <v>6</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Buckland Belle</t>
+          <t>Betty Lemon</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>3</v>
       </c>
       <c r="J71" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="K71" t="n">
         <v>53</v>
@@ -4628,14 +4520,16 @@
       <c r="M71" t="n">
         <v>99.64</v>
       </c>
-      <c r="N71" t="inlineStr"/>
+      <c r="N71" t="n">
+        <v>55.3</v>
+      </c>
       <c r="O71" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4664,28 +4558,30 @@
         <v>6</v>
       </c>
       <c r="G72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Betty Lemon</t>
+          <t>Scarfo (IRE)</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J72" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="K72" t="n">
-        <v>53</v>
-      </c>
-      <c r="L72" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="L72" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M72" t="n">
         <v>99.64</v>
       </c>
       <c r="N72" t="n">
-        <v>58.7</v>
+        <v>46.7</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4693,7 +4589,7 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="73">
@@ -4722,30 +4618,30 @@
         <v>6</v>
       </c>
       <c r="G73" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Scarfo (IRE)</t>
+          <t>Typeface</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J73" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K73" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L73" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="M73" t="n">
         <v>99.64</v>
       </c>
       <c r="N73" t="n">
-        <v>53.9</v>
+        <v>54.6</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4753,7 +4649,7 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4782,30 +4678,30 @@
         <v>6</v>
       </c>
       <c r="G74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Typeface</t>
+          <t>Angels Call (IRE)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J74" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K74" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="L74" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="M74" t="n">
         <v>99.64</v>
       </c>
       <c r="N74" t="n">
-        <v>54.6</v>
+        <v>49.5</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -4813,7 +4709,7 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4842,30 +4738,30 @@
         <v>6</v>
       </c>
       <c r="G75" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Angels Call (IRE)</t>
+          <t>Racing Demon</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J75" t="n">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="K75" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="L75" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="M75" t="n">
         <v>99.64</v>
       </c>
       <c r="N75" t="n">
-        <v>49.5</v>
+        <v>52</v>
       </c>
       <c r="O75" t="inlineStr">
         <is>
@@ -4873,7 +4769,7 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4902,30 +4798,30 @@
         <v>6</v>
       </c>
       <c r="G76" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Racing Demon</t>
+          <t>Eye Of The Water (IRE)</t>
         </is>
       </c>
       <c r="I76" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J76" t="n">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K76" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="L76" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="M76" t="n">
         <v>99.64</v>
       </c>
       <c r="N76" t="n">
-        <v>52</v>
+        <v>43.3</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -4933,7 +4829,7 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77">
@@ -4962,30 +4858,30 @@
         <v>6</v>
       </c>
       <c r="G77" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Eye Of The Water (IRE)</t>
+          <t>Mooretown Lad (IRE)</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J77" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="K77" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L77" t="n">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="M77" t="n">
         <v>99.64</v>
       </c>
       <c r="N77" t="n">
-        <v>43.3</v>
+        <v>45.7</v>
       </c>
       <c r="O77" t="inlineStr">
         <is>
@@ -4993,7 +4889,7 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -5022,30 +4918,30 @@
         <v>6</v>
       </c>
       <c r="G78" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Mooretown Lad (IRE)</t>
+          <t>Uncle Albert (IRE)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J78" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K78" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="L78" t="n">
-        <v>4.45</v>
+        <v>12.45</v>
       </c>
       <c r="M78" t="n">
         <v>99.64</v>
       </c>
       <c r="N78" t="n">
-        <v>45.7</v>
+        <v>25.8</v>
       </c>
       <c r="O78" t="inlineStr">
         <is>
@@ -5053,7 +4949,7 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -5082,34 +4978,34 @@
         <v>6</v>
       </c>
       <c r="G79" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Uncle Albert (IRE)</t>
+          <t>Sorted (IRE)</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J79" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="K79" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L79" t="n">
-        <v>12.45</v>
+        <v>24.45</v>
       </c>
       <c r="M79" t="n">
         <v>99.64</v>
       </c>
       <c r="N79" t="n">
-        <v>25.8</v>
+        <v>18.6</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P79" t="n">
@@ -5142,30 +5038,30 @@
         <v>6</v>
       </c>
       <c r="G80" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sorted (IRE)</t>
+          <t>Beau Chevalier</t>
         </is>
       </c>
       <c r="I80" t="n">
         <v>3</v>
       </c>
       <c r="J80" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="K80" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="L80" t="n">
-        <v>24.45</v>
+        <v>34.45</v>
       </c>
       <c r="M80" t="n">
         <v>99.64</v>
       </c>
       <c r="N80" t="n">
-        <v>18.6</v>
+        <v>-0.1</v>
       </c>
       <c r="O80" t="inlineStr">
         <is>
@@ -5201,40 +5097,24 @@
       <c r="F81" t="n">
         <v>6</v>
       </c>
-      <c r="G81" t="n">
-        <v>10</v>
-      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Beau Chevalier</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>3</v>
-      </c>
-      <c r="J81" t="n">
-        <v>119</v>
-      </c>
-      <c r="K81" t="n">
-        <v>46</v>
-      </c>
-      <c r="L81" t="n">
-        <v>34.45</v>
-      </c>
-      <c r="M81" t="n">
-        <v>99.64</v>
-      </c>
-      <c r="N81" t="n">
-        <v>-0.1</v>
-      </c>
+          <t>Buckland Belle</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P81" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5711,7 +5591,7 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -5751,7 +5631,7 @@
         <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K90" t="n">
         <v>42</v>
@@ -5763,7 +5643,7 @@
         <v>127.7</v>
       </c>
       <c r="N90" t="n">
-        <v>17.7</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="O90" t="inlineStr">
         <is>
@@ -5771,7 +5651,7 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
@@ -6129,7 +6009,7 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -6169,7 +6049,7 @@
         <v>9</v>
       </c>
       <c r="J97" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K97" t="n">
         <v>62</v>
@@ -6181,7 +6061,7 @@
         <v>127.47</v>
       </c>
       <c r="N97" t="n">
-        <v>46</v>
+        <v>40.3</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
@@ -6189,7 +6069,7 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="98">
@@ -6249,7 +6129,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -7832,34 +7712,36 @@
         <v>5</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Aigeas (FR)</t>
+          <t>Bami (IRE)</t>
         </is>
       </c>
       <c r="I125" t="n">
         <v>3</v>
       </c>
       <c r="J125" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K125" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="n">
         <v>83.31</v>
       </c>
-      <c r="N125" t="inlineStr"/>
+      <c r="N125" t="n">
+        <v>76.3</v>
+      </c>
       <c r="O125" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>-14.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="126">
@@ -7888,34 +7770,38 @@
         <v>5</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>White Ladder (IRE)</t>
+          <t>Documenting</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J126" t="n">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="K126" t="n">
-        <v>60</v>
-      </c>
-      <c r="L126" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M126" t="n">
         <v>83.31</v>
       </c>
-      <c r="N126" t="inlineStr"/>
+      <c r="N126" t="n">
+        <v>76.90000000000001</v>
+      </c>
       <c r="O126" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>-14.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
@@ -7944,34 +7830,38 @@
         <v>5</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Trinculo</t>
+          <t>Ararat (IRE)</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J127" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K127" t="n">
         <v>69</v>
       </c>
-      <c r="L127" t="inlineStr"/>
+      <c r="L127" t="n">
+        <v>2.25</v>
+      </c>
       <c r="M127" t="n">
         <v>83.31</v>
       </c>
-      <c r="N127" t="inlineStr"/>
+      <c r="N127" t="n">
+        <v>70.5</v>
+      </c>
       <c r="O127" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>-14.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="128">
@@ -8000,34 +7890,38 @@
         <v>5</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Seeing Stars</t>
+          <t>Lahan Kingman (IRE)</t>
         </is>
       </c>
       <c r="I128" t="n">
         <v>3</v>
       </c>
       <c r="J128" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K128" t="n">
-        <v>68</v>
-      </c>
-      <c r="L128" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="L128" t="n">
+        <v>2.4</v>
+      </c>
       <c r="M128" t="n">
         <v>83.31</v>
       </c>
-      <c r="N128" t="inlineStr"/>
+      <c r="N128" t="n">
+        <v>69.90000000000001</v>
+      </c>
       <c r="O128" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>-14.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="129">
@@ -8056,28 +7950,30 @@
         <v>5</v>
       </c>
       <c r="G129" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Bami (IRE)</t>
+          <t>Signcastle City (IRE)</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J129" t="n">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="K129" t="n">
-        <v>70</v>
-      </c>
-      <c r="L129" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="L129" t="n">
+        <v>2.55</v>
+      </c>
       <c r="M129" t="n">
         <v>83.31</v>
       </c>
       <c r="N129" t="n">
-        <v>76.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="O129" t="inlineStr">
         <is>
@@ -8085,7 +7981,7 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -8114,30 +8010,30 @@
         <v>5</v>
       </c>
       <c r="G130" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Documenting</t>
+          <t>Nakaaha</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J130" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K130" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L130" t="n">
-        <v>0.75</v>
+        <v>5.550000000000001</v>
       </c>
       <c r="M130" t="n">
         <v>83.31</v>
       </c>
       <c r="N130" t="n">
-        <v>76.90000000000001</v>
+        <v>64.2</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
@@ -8145,7 +8041,7 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -8174,30 +8070,30 @@
         <v>5</v>
       </c>
       <c r="G131" t="n">
+        <v>7</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Creative Queen (USA)</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
         <v>3</v>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Ararat (IRE)</t>
-        </is>
-      </c>
-      <c r="I131" t="n">
-        <v>6</v>
-      </c>
       <c r="J131" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="K131" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="L131" t="n">
-        <v>2.25</v>
+        <v>7.050000000000001</v>
       </c>
       <c r="M131" t="n">
         <v>83.31</v>
       </c>
       <c r="N131" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -8205,7 +8101,7 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="132">
@@ -8234,30 +8130,30 @@
         <v>5</v>
       </c>
       <c r="G132" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Lahan Kingman (IRE)</t>
+          <t>Noodle Mission (USA)</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J132" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="K132" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="L132" t="n">
-        <v>2.4</v>
+        <v>7.15</v>
       </c>
       <c r="M132" t="n">
         <v>83.31</v>
       </c>
       <c r="N132" t="n">
-        <v>69.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="O132" t="inlineStr">
         <is>
@@ -8265,7 +8161,7 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -8294,30 +8190,30 @@
         <v>5</v>
       </c>
       <c r="G133" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Signcastle City (IRE)</t>
+          <t>Sedgemoor (IRE)</t>
         </is>
       </c>
       <c r="I133" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J133" t="n">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="K133" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="L133" t="n">
-        <v>2.55</v>
+        <v>11.65</v>
       </c>
       <c r="M133" t="n">
         <v>83.31</v>
       </c>
       <c r="N133" t="n">
-        <v>72.09999999999999</v>
+        <v>35.3</v>
       </c>
       <c r="O133" t="inlineStr">
         <is>
@@ -8325,7 +8221,7 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="134">
@@ -8354,30 +8250,30 @@
         <v>5</v>
       </c>
       <c r="G134" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Nakaaha</t>
+          <t>Starlight Sami (IRE)</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J134" t="n">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="K134" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L134" t="n">
-        <v>5.55</v>
+        <v>12.15</v>
       </c>
       <c r="M134" t="n">
         <v>83.31</v>
       </c>
       <c r="N134" t="n">
-        <v>64.2</v>
+        <v>42.7</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -8385,7 +8281,7 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -8414,30 +8310,30 @@
         <v>5</v>
       </c>
       <c r="G135" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Creative Queen (USA)</t>
+          <t>Havana Halo</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J135" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K135" t="n">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="L135" t="n">
-        <v>7.05</v>
+        <v>14.4</v>
       </c>
       <c r="M135" t="n">
         <v>83.31</v>
       </c>
       <c r="N135" t="n">
-        <v>60</v>
+        <v>39.6</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -8445,7 +8341,7 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
@@ -8474,38 +8370,38 @@
         <v>5</v>
       </c>
       <c r="G136" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Noodle Mission (USA)</t>
+          <t>Dakota Breeze (IRE)</t>
         </is>
       </c>
       <c r="I136" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J136" t="n">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="K136" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="L136" t="n">
-        <v>7.149999999999999</v>
+        <v>27.4</v>
       </c>
       <c r="M136" t="n">
         <v>83.31</v>
       </c>
       <c r="N136" t="n">
-        <v>61</v>
+        <v>24.4</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -8533,40 +8429,24 @@
       <c r="F137" t="n">
         <v>5</v>
       </c>
-      <c r="G137" t="n">
-        <v>9</v>
-      </c>
+      <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Sedgemoor (IRE)</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>5</v>
-      </c>
-      <c r="J137" t="n">
-        <v>123</v>
-      </c>
-      <c r="K137" t="n">
-        <v>56</v>
-      </c>
-      <c r="L137" t="n">
-        <v>11.65</v>
-      </c>
-      <c r="M137" t="n">
-        <v>83.31</v>
-      </c>
-      <c r="N137" t="n">
-        <v>35.3</v>
-      </c>
+          <t>Trinculo</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P137" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8593,40 +8473,24 @@
       <c r="F138" t="n">
         <v>5</v>
       </c>
-      <c r="G138" t="n">
-        <v>10</v>
-      </c>
+      <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Starlight Sami (IRE)</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>3</v>
-      </c>
-      <c r="J138" t="n">
-        <v>129</v>
-      </c>
-      <c r="K138" t="n">
-        <v>71</v>
-      </c>
-      <c r="L138" t="n">
-        <v>12.15</v>
-      </c>
-      <c r="M138" t="n">
-        <v>83.31</v>
-      </c>
-      <c r="N138" t="n">
-        <v>42.7</v>
-      </c>
+          <t>Aigeas (FR)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P138" t="n">
-        <v>1</v>
-      </c>
+      <c r="P138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -8653,40 +8517,24 @@
       <c r="F139" t="n">
         <v>5</v>
       </c>
-      <c r="G139" t="n">
-        <v>11</v>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Havana Halo</t>
-        </is>
-      </c>
-      <c r="I139" t="n">
-        <v>4</v>
-      </c>
-      <c r="J139" t="n">
-        <v>135</v>
-      </c>
-      <c r="K139" t="n">
-        <v>68</v>
-      </c>
-      <c r="L139" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="M139" t="n">
-        <v>83.31</v>
-      </c>
-      <c r="N139" t="n">
-        <v>39.6</v>
-      </c>
+          <t>White Ladder (IRE)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P139" t="n">
-        <v>1</v>
-      </c>
+      <c r="P139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -8713,40 +8561,24 @@
       <c r="F140" t="n">
         <v>5</v>
       </c>
-      <c r="G140" t="n">
-        <v>12</v>
-      </c>
+      <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Dakota Breeze (IRE)</t>
-        </is>
-      </c>
-      <c r="I140" t="n">
-        <v>3</v>
-      </c>
-      <c r="J140" t="n">
-        <v>127</v>
-      </c>
-      <c r="K140" t="n">
-        <v>69</v>
-      </c>
-      <c r="L140" t="n">
-        <v>27.4</v>
-      </c>
-      <c r="M140" t="n">
-        <v>83.31</v>
-      </c>
-      <c r="N140" t="n">
-        <v>24.4</v>
-      </c>
+          <t>Seeing Stars</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P140" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -8774,34 +8606,36 @@
         <v>5</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Escape Plan</t>
+          <t>Rage Of Thunder (IRE)</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J141" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="K141" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="n">
         <v>70.42</v>
       </c>
-      <c r="N141" t="inlineStr"/>
+      <c r="N141" t="n">
+        <v>85.90000000000001</v>
+      </c>
       <c r="O141" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P141" t="n">
-        <v>-13.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
@@ -8830,15 +8664,15 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Albert Cee (FR)</t>
+          <t>Monsieur Patat</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J142" t="n">
         <v>135</v>
@@ -8846,18 +8680,22 @@
       <c r="K142" t="n">
         <v>63</v>
       </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="L142" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M142" t="n">
         <v>70.42</v>
       </c>
-      <c r="N142" t="inlineStr"/>
+      <c r="N142" t="n">
+        <v>79</v>
+      </c>
       <c r="O142" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>-13.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
@@ -8886,28 +8724,30 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Rage Of Thunder (IRE)</t>
+          <t>Roman Spring (IRE)</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J143" t="n">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="K143" t="n">
-        <v>69</v>
-      </c>
-      <c r="L143" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L143" t="n">
+        <v>3</v>
+      </c>
       <c r="M143" t="n">
         <v>70.42</v>
       </c>
       <c r="N143" t="n">
-        <v>85.90000000000001</v>
+        <v>61</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -8915,7 +8755,7 @@
         </is>
       </c>
       <c r="P143" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="144">
@@ -8944,30 +8784,30 @@
         <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Monsieur Patat</t>
+          <t>Yes Waliim (IRE)</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J144" t="n">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K144" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="L144" t="n">
-        <v>0.5</v>
+        <v>4.75</v>
       </c>
       <c r="M144" t="n">
         <v>70.42</v>
       </c>
       <c r="N144" t="n">
-        <v>79</v>
+        <v>62.5</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -8975,7 +8815,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="145">
@@ -9004,30 +8844,30 @@
         <v>5</v>
       </c>
       <c r="G145" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Roman Spring (IRE)</t>
+          <t>Massimo Blue</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J145" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="K145" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L145" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="M145" t="n">
         <v>70.42</v>
       </c>
       <c r="N145" t="n">
-        <v>65.2</v>
+        <v>69.3</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -9035,7 +8875,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -9064,30 +8904,30 @@
         <v>5</v>
       </c>
       <c r="G146" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Yes Waliim (IRE)</t>
+          <t>Forever My Prince</t>
         </is>
       </c>
       <c r="I146" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J146" t="n">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="K146" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="L146" t="n">
-        <v>4.75</v>
+        <v>5.3</v>
       </c>
       <c r="M146" t="n">
         <v>70.42</v>
       </c>
       <c r="N146" t="n">
-        <v>62.5</v>
+        <v>63.7</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -9095,7 +8935,7 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>-3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
@@ -9124,30 +8964,30 @@
         <v>5</v>
       </c>
       <c r="G147" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Massimo Blue</t>
+          <t>The Caribbean (IRE)</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J147" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K147" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L147" t="n">
-        <v>4.8</v>
+        <v>6.3</v>
       </c>
       <c r="M147" t="n">
         <v>70.42</v>
       </c>
       <c r="N147" t="n">
-        <v>69.3</v>
+        <v>63.4</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -9184,30 +9024,30 @@
         <v>5</v>
       </c>
       <c r="G148" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Forever My Prince</t>
+          <t>Laughterintherain (FR)</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J148" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K148" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="L148" t="n">
-        <v>5.3</v>
+        <v>7.3</v>
       </c>
       <c r="M148" t="n">
         <v>70.42</v>
       </c>
       <c r="N148" t="n">
-        <v>63.7</v>
+        <v>58</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9215,7 +9055,7 @@
         </is>
       </c>
       <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -9244,30 +9084,30 @@
         <v>5</v>
       </c>
       <c r="G149" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>The Caribbean (IRE)</t>
+          <t>Arjack</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J149" t="n">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="K149" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="L149" t="n">
-        <v>6.3</v>
+        <v>10.3</v>
       </c>
       <c r="M149" t="n">
         <v>70.42</v>
       </c>
       <c r="N149" t="n">
-        <v>63.4</v>
+        <v>42.9</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -9275,7 +9115,7 @@
         </is>
       </c>
       <c r="P149" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="150">
@@ -9304,30 +9144,30 @@
         <v>5</v>
       </c>
       <c r="G150" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Laughterintherain (FR)</t>
+          <t>Exhibitioning</t>
         </is>
       </c>
       <c r="I150" t="n">
         <v>3</v>
       </c>
       <c r="J150" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="K150" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L150" t="n">
-        <v>7.3</v>
+        <v>12.3</v>
       </c>
       <c r="M150" t="n">
         <v>70.42</v>
       </c>
       <c r="N150" t="n">
-        <v>58</v>
+        <v>44.9</v>
       </c>
       <c r="O150" t="inlineStr">
         <is>
@@ -9335,7 +9175,7 @@
         </is>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="151">
@@ -9364,30 +9204,30 @@
         <v>5</v>
       </c>
       <c r="G151" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Arjack</t>
+          <t>Twirler</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J151" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K151" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="L151" t="n">
-        <v>10.3</v>
+        <v>17.05</v>
       </c>
       <c r="M151" t="n">
         <v>70.42</v>
       </c>
       <c r="N151" t="n">
-        <v>42.9</v>
+        <v>29.3</v>
       </c>
       <c r="O151" t="inlineStr">
         <is>
@@ -9395,7 +9235,7 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -9424,38 +9264,38 @@
         <v>5</v>
       </c>
       <c r="G152" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Exhibitioning</t>
+          <t>Obsidian Dream</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J152" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K152" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="L152" t="n">
-        <v>12.3</v>
+        <v>36.05</v>
       </c>
       <c r="M152" t="n">
         <v>70.42</v>
       </c>
       <c r="N152" t="n">
-        <v>44.9</v>
+        <v>15.7</v>
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
@@ -9483,40 +9323,24 @@
       <c r="F153" t="n">
         <v>5</v>
       </c>
-      <c r="G153" t="n">
-        <v>11</v>
-      </c>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Twirler</t>
-        </is>
-      </c>
-      <c r="I153" t="n">
-        <v>5</v>
-      </c>
-      <c r="J153" t="n">
-        <v>142</v>
-      </c>
-      <c r="K153" t="n">
-        <v>70</v>
-      </c>
-      <c r="L153" t="n">
-        <v>17.05</v>
-      </c>
-      <c r="M153" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="N153" t="n">
-        <v>33</v>
-      </c>
+          <t>Albert Cee (FR)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="O153" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P153" t="n">
-        <v>0</v>
-      </c>
+      <c r="P153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -9543,40 +9367,24 @@
       <c r="F154" t="n">
         <v>5</v>
       </c>
-      <c r="G154" t="n">
-        <v>12</v>
-      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Obsidian Dream</t>
-        </is>
-      </c>
-      <c r="I154" t="n">
-        <v>4</v>
-      </c>
-      <c r="J154" t="n">
-        <v>142</v>
-      </c>
-      <c r="K154" t="n">
-        <v>70</v>
-      </c>
-      <c r="L154" t="n">
-        <v>36.05</v>
-      </c>
-      <c r="M154" t="n">
-        <v>70.42</v>
-      </c>
-      <c r="N154" t="n">
-        <v>15.5</v>
-      </c>
+          <t>Escape Plan</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P154" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -9604,34 +9412,36 @@
         <v>4</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Kitty Foyle (IRE)</t>
+          <t>Baileys Khelstar (FR)</t>
         </is>
       </c>
       <c r="I155" t="n">
         <v>6</v>
       </c>
       <c r="J155" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K155" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" t="n">
         <v>208.02</v>
       </c>
-      <c r="N155" t="inlineStr"/>
+      <c r="N155" t="n">
+        <v>78.40000000000001</v>
+      </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P155" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -9660,34 +9470,38 @@
         <v>4</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Taritino (IRE)</t>
+          <t>Almuhit (IRE)</t>
         </is>
       </c>
       <c r="I156" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J156" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="K156" t="n">
-        <v>72</v>
-      </c>
-      <c r="L156" t="inlineStr"/>
+        <v>83</v>
+      </c>
+      <c r="L156" t="n">
+        <v>2.75</v>
+      </c>
       <c r="M156" t="n">
         <v>208.02</v>
       </c>
-      <c r="N156" t="inlineStr"/>
+      <c r="N156" t="n">
+        <v>71.8</v>
+      </c>
       <c r="O156" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P156" t="n">
-        <v>-4.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
@@ -9716,28 +9530,30 @@
         <v>4</v>
       </c>
       <c r="G157" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Baileys Khelstar (FR)</t>
+          <t>Russian Rumour (IRE)</t>
         </is>
       </c>
       <c r="I157" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J157" t="n">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="K157" t="n">
-        <v>78</v>
-      </c>
-      <c r="L157" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="L157" t="n">
+        <v>6.5</v>
+      </c>
       <c r="M157" t="n">
         <v>208.02</v>
       </c>
       <c r="N157" t="n">
-        <v>78.40000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="O157" t="inlineStr">
         <is>
@@ -9773,40 +9589,24 @@
       <c r="F158" t="n">
         <v>4</v>
       </c>
-      <c r="G158" t="n">
-        <v>2</v>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Almuhit (IRE)</t>
-        </is>
-      </c>
-      <c r="I158" t="n">
-        <v>7</v>
-      </c>
-      <c r="J158" t="n">
-        <v>141</v>
-      </c>
-      <c r="K158" t="n">
-        <v>83</v>
-      </c>
-      <c r="L158" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="M158" t="n">
-        <v>208.02</v>
-      </c>
-      <c r="N158" t="n">
-        <v>75.3</v>
-      </c>
+          <t>Taritino (IRE)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P158" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -9833,40 +9633,24 @@
       <c r="F159" t="n">
         <v>4</v>
       </c>
-      <c r="G159" t="n">
-        <v>3</v>
-      </c>
+      <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Russian Rumour (IRE)</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>9</v>
-      </c>
-      <c r="J159" t="n">
-        <v>137</v>
-      </c>
-      <c r="K159" t="n">
-        <v>79</v>
-      </c>
-      <c r="L159" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="M159" t="n">
-        <v>208.02</v>
-      </c>
-      <c r="N159" t="n">
-        <v>64.90000000000001</v>
-      </c>
+          <t>Kitty Foyle (IRE)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P159" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9894,34 +9678,36 @@
         <v>5</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Tiger (FR)</t>
+          <t>Redbud Sixteen (IRE)</t>
         </is>
       </c>
       <c r="I160" t="n">
         <v>4</v>
       </c>
       <c r="J160" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K160" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="n">
         <v>135.76</v>
       </c>
-      <c r="N160" t="inlineStr"/>
+      <c r="N160" t="n">
+        <v>82.59999999999999</v>
+      </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P160" t="n">
-        <v>-10.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -9950,34 +9736,38 @@
         <v>5</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Harlington (FR)</t>
+          <t>Raintown (IRE)</t>
         </is>
       </c>
       <c r="I161" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J161" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="K161" t="n">
-        <v>72</v>
-      </c>
-      <c r="L161" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="L161" t="n">
+        <v>6</v>
+      </c>
       <c r="M161" t="n">
         <v>135.76</v>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>58</v>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>-10.5</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="162">
@@ -10006,15 +9796,15 @@
         <v>5</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Redbud Sixteen (IRE)</t>
+          <t>Shady Bay (IRE)</t>
         </is>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J162" t="n">
         <v>138</v>
@@ -10022,12 +9812,14 @@
       <c r="K162" t="n">
         <v>75</v>
       </c>
-      <c r="L162" t="inlineStr"/>
+      <c r="L162" t="n">
+        <v>6.75</v>
+      </c>
       <c r="M162" t="n">
         <v>135.76</v>
       </c>
       <c r="N162" t="n">
-        <v>83.7</v>
+        <v>70.5</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -10035,7 +9827,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -10064,30 +9856,30 @@
         <v>5</v>
       </c>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Raintown (IRE)</t>
+          <t>Brodies Boy (FR)</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J163" t="n">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K163" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="L163" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="M163" t="n">
         <v>135.76</v>
       </c>
       <c r="N163" t="n">
-        <v>62.8</v>
+        <v>56.5</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -10095,7 +9887,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="164">
@@ -10124,30 +9916,30 @@
         <v>5</v>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Shady Bay (IRE)</t>
+          <t>Expressionless</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J164" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="K164" t="n">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="L164" t="n">
-        <v>6.75</v>
+        <v>8</v>
       </c>
       <c r="M164" t="n">
         <v>135.76</v>
       </c>
       <c r="N164" t="n">
-        <v>70.5</v>
+        <v>67.3</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -10155,7 +9947,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="165">
@@ -10184,30 +9976,30 @@
         <v>5</v>
       </c>
       <c r="G165" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Brodies Boy (FR)</t>
+          <t>Grey Fox (IRE)</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J165" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="K165" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L165" t="n">
-        <v>7.5</v>
+        <v>9.25</v>
       </c>
       <c r="M165" t="n">
         <v>135.76</v>
       </c>
       <c r="N165" t="n">
-        <v>58.4</v>
+        <v>60.1</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10215,7 +10007,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="166">
@@ -10244,30 +10036,30 @@
         <v>5</v>
       </c>
       <c r="G166" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Expressionless</t>
+          <t>Yokohama (IRE)</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J166" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K166" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="L166" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="M166" t="n">
         <v>135.76</v>
       </c>
       <c r="N166" t="n">
-        <v>67.3</v>
+        <v>57.4</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10275,7 +10067,7 @@
         </is>
       </c>
       <c r="P166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
@@ -10304,30 +10096,30 @@
         <v>5</v>
       </c>
       <c r="G167" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Grey Fox (IRE)</t>
+          <t>Robusto (IRE)</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J167" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K167" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L167" t="n">
-        <v>9.25</v>
+        <v>25.5</v>
       </c>
       <c r="M167" t="n">
         <v>135.76</v>
       </c>
       <c r="N167" t="n">
-        <v>60.1</v>
+        <v>54</v>
       </c>
       <c r="O167" t="inlineStr">
         <is>
@@ -10335,7 +10127,7 @@
         </is>
       </c>
       <c r="P167" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="168">
@@ -10364,30 +10156,30 @@
         <v>5</v>
       </c>
       <c r="G168" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Yokohama (IRE)</t>
+          <t>Vino Sauro (USA)</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J168" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K168" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L168" t="n">
-        <v>13.5</v>
+        <v>27</v>
       </c>
       <c r="M168" t="n">
         <v>135.76</v>
       </c>
       <c r="N168" t="n">
-        <v>57.4</v>
+        <v>54.5</v>
       </c>
       <c r="O168" t="inlineStr">
         <is>
@@ -10395,7 +10187,7 @@
         </is>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -10423,40 +10215,24 @@
       <c r="F169" t="n">
         <v>5</v>
       </c>
-      <c r="G169" t="n">
-        <v>8</v>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Robusto (IRE)</t>
-        </is>
-      </c>
-      <c r="I169" t="n">
-        <v>6</v>
-      </c>
-      <c r="J169" t="n">
-        <v>132</v>
-      </c>
-      <c r="K169" t="n">
-        <v>69</v>
-      </c>
-      <c r="L169" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="M169" t="n">
-        <v>135.76</v>
-      </c>
-      <c r="N169" t="n">
-        <v>54</v>
-      </c>
+          <t>Tiger (FR)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
       <c r="O169" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P169" t="n">
-        <v>-1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10483,40 +10259,24 @@
       <c r="F170" t="n">
         <v>5</v>
       </c>
-      <c r="G170" t="n">
-        <v>9</v>
-      </c>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Vino Sauro (USA)</t>
-        </is>
-      </c>
-      <c r="I170" t="n">
-        <v>4</v>
-      </c>
-      <c r="J170" t="n">
-        <v>138</v>
-      </c>
-      <c r="K170" t="n">
-        <v>75</v>
-      </c>
-      <c r="L170" t="n">
-        <v>27</v>
-      </c>
-      <c r="M170" t="n">
-        <v>135.76</v>
-      </c>
-      <c r="N170" t="n">
-        <v>56.4</v>
-      </c>
+          <t>Harlington (FR)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr"/>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr">
         <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="P170" t="n">
-        <v>1</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
